--- a/research/traditional_assets/database/data/vietnam/vietnam_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ16"/>
+  <dimension ref="A1:AQ13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.283</v>
+        <v>0.275</v>
       </c>
       <c r="E2">
-        <v>0.398</v>
+        <v>0.354</v>
       </c>
       <c r="F2">
-        <v>0.244</v>
+        <v>0.215</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>2.661597711640345e-05</v>
+        <v>-0.0002477988421735095</v>
       </c>
       <c r="J2">
-        <v>2.124205180405127e-05</v>
+        <v>-0.0001970528828321283</v>
       </c>
       <c r="K2">
-        <v>5445.1</v>
+        <v>5674.7</v>
       </c>
       <c r="L2">
-        <v>0.426167536726436</v>
+        <v>0.4574710790438953</v>
       </c>
       <c r="M2">
-        <v>358.763</v>
+        <v>197.815</v>
       </c>
       <c r="N2">
-        <v>0.004942762473564929</v>
+        <v>0.005388542180260036</v>
       </c>
       <c r="O2">
-        <v>0.06588731152779563</v>
+        <v>0.03485911149488079</v>
       </c>
       <c r="P2">
-        <v>356.642</v>
+        <v>197.815</v>
       </c>
       <c r="Q2">
-        <v>0.004913540956277941</v>
+        <v>0.005388542180260036</v>
       </c>
       <c r="R2">
-        <v>0.06549778700115699</v>
+        <v>0.03485911149488079</v>
       </c>
       <c r="S2">
-        <v>2.121</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.005911980889891097</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>29746.8</v>
+        <v>35676.4</v>
       </c>
       <c r="V2">
-        <v>0.4098286800719171</v>
+        <v>0.9718362421445752</v>
       </c>
       <c r="W2">
-        <v>0.2373043186871397</v>
+        <v>0.2603667602841566</v>
       </c>
       <c r="X2">
-        <v>0.08083243970550137</v>
+        <v>0.1544958509315746</v>
       </c>
       <c r="Y2">
-        <v>0.1564718789816383</v>
+        <v>0.105870909352582</v>
       </c>
       <c r="Z2">
-        <v>0.5213728286629544</v>
+        <v>0.2959913300587182</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06819264226434288</v>
+        <v>0.1005356670610681</v>
       </c>
       <c r="AC2">
-        <v>-0.06835096437645662</v>
+        <v>-0.1005356670610681</v>
       </c>
       <c r="AD2">
-        <v>38746.83</v>
+        <v>44255.4</v>
       </c>
       <c r="AE2">
-        <v>343.5496516099071</v>
+        <v>150.9191036887065</v>
       </c>
       <c r="AF2">
-        <v>39090.37965160991</v>
+        <v>44406.31910368871</v>
       </c>
       <c r="AG2">
-        <v>9343.579651609911</v>
+        <v>8729.919103688706</v>
       </c>
       <c r="AH2">
-        <v>0.3500404908789821</v>
+        <v>0.5474379922926221</v>
       </c>
       <c r="AI2">
-        <v>0.5565926303455122</v>
+        <v>0.5930986978166091</v>
       </c>
       <c r="AJ2">
-        <v>0.1140475126337096</v>
+        <v>0.1921187722217659</v>
       </c>
       <c r="AK2">
-        <v>0.2307924047510125</v>
+        <v>0.2227286141131869</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>561.1416364952934</v>
+        <v>1632.43821468093</v>
       </c>
       <c r="AP2">
-        <v>135.3161426735686</v>
+        <v>322.0184103168095</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Saigon Thuong Tin Commercial Joint Stock Bank (HOSE:STB)</t>
+          <t>Joint Stock Commercial Bank for Investment and Development of Vietnam (HOSE:BID)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,7 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.3</v>
+        <v>0.132</v>
+      </c>
+      <c r="E3">
+        <v>0.232</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,34 +731,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.02452071591898442</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.01949855859440098</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>148.7</v>
+        <v>678.6</v>
       </c>
       <c r="L3">
-        <v>0.2163853317811408</v>
+        <v>0.3881928951432985</v>
       </c>
       <c r="M3">
-        <v>0.005</v>
+        <v>37.6</v>
       </c>
       <c r="N3">
-        <v>1.913582609361246e-06</v>
+        <v>0.004584862637027644</v>
       </c>
       <c r="O3">
-        <v>3.362474781439139e-05</v>
+        <v>0.05540819333922782</v>
       </c>
       <c r="P3">
-        <v>0.005</v>
+        <v>37.6</v>
       </c>
       <c r="Q3">
-        <v>1.913582609361246e-06</v>
+        <v>0.004584862637027644</v>
       </c>
       <c r="R3">
-        <v>3.362474781439139e-05</v>
+        <v>0.05540819333922782</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,67 +767,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>810.4</v>
+        <v>10304.6</v>
       </c>
       <c r="V3">
-        <v>0.3101534693252708</v>
+        <v>1.256520625784975</v>
       </c>
       <c r="W3">
-        <v>0.122235922729141</v>
+        <v>0.1867569352708058</v>
       </c>
       <c r="X3">
-        <v>0.07558756618312995</v>
+        <v>0.1089272133223186</v>
       </c>
       <c r="Y3">
-        <v>0.04664835654601102</v>
+        <v>0.07782972194848727</v>
       </c>
       <c r="Z3">
-        <v>0.8853994916958651</v>
+        <v>0.2319019381541768</v>
       </c>
       <c r="AA3">
-        <v>0.01726401386828467</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06564813382068217</v>
+        <v>0.09449878117410376</v>
       </c>
       <c r="AC3">
-        <v>-0.0483841199523975</v>
+        <v>-0.09449878117410376</v>
       </c>
       <c r="AD3">
-        <v>923.6</v>
+        <v>4349.1</v>
       </c>
       <c r="AE3">
-        <v>232.2468201023695</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>1155.84682010237</v>
+        <v>4349.1</v>
       </c>
       <c r="AG3">
-        <v>345.4468201023695</v>
+        <v>-5955.5</v>
       </c>
       <c r="AH3">
-        <v>0.3066926156825185</v>
+        <v>0.3465418326693228</v>
       </c>
       <c r="AI3">
-        <v>0.441104517629164</v>
+        <v>0.5069471966429654</v>
       </c>
       <c r="AJ3">
-        <v>0.1167702237462529</v>
+        <v>-2.652311392179568</v>
       </c>
       <c r="AK3">
-        <v>0.1908602044356371</v>
+        <v>3.451263328697264</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>14.59083728278041</v>
-      </c>
-      <c r="AP3">
-        <v>5.457295736214369</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vietnam Export Import Commercial Joint Stock Bank (HOSE:EIB)</t>
+          <t>Asia Commercial Joint Stock Bank (HOSE:ACB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,7 +841,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.128</v>
+        <v>0.283</v>
+      </c>
+      <c r="E4">
+        <v>0.482</v>
+      </c>
+      <c r="F4">
+        <v>0.21</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,10 +862,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>42.7</v>
+        <v>555.2</v>
       </c>
       <c r="L4">
-        <v>0.2690611216131065</v>
+        <v>0.5126973866469665</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,55 +889,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1265.7</v>
+        <v>2749.7</v>
       </c>
       <c r="V4">
-        <v>0.6942951179374658</v>
+        <v>0.8851155604197515</v>
       </c>
       <c r="W4">
-        <v>0.0596535345068455</v>
+        <v>0.2979020228577561</v>
       </c>
       <c r="X4">
-        <v>0.05980296660935877</v>
+        <v>0.1127032840423185</v>
       </c>
       <c r="Y4">
-        <v>-0.0001494321025132736</v>
+        <v>0.1851987388154376</v>
       </c>
       <c r="Z4">
-        <v>-0.5347035040431265</v>
+        <v>0.48221044663134</v>
       </c>
       <c r="AA4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05980439361583285</v>
+        <v>0.0952169777896979</v>
       </c>
       <c r="AC4">
-        <v>-0.05980439361583285</v>
+        <v>-0.0952169777896979</v>
       </c>
       <c r="AD4">
-        <v>1.33</v>
+        <v>1945.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.33</v>
+        <v>1945.3</v>
       </c>
       <c r="AG4">
-        <v>-1264.37</v>
+        <v>-804.3999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.0007290347689288671</v>
+        <v>0.3850630455868089</v>
       </c>
       <c r="AI4">
-        <v>0.001715177385450653</v>
+        <v>0.4543819489862655</v>
       </c>
       <c r="AJ4">
-        <v>-2.263340672717184</v>
+        <v>-0.3494049170358787</v>
       </c>
       <c r="AK4">
-        <v>2.578925897974585</v>
+        <v>-0.5252366960496244</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Joint Stock Commercial Bank for Foreign Trade of Vietnam (HOSE:VCB)</t>
+          <t>Saigon Thuong Tin Commercial Joint Stock Bank (HOSE:STB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,13 +963,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.193</v>
+        <v>0.181</v>
       </c>
       <c r="E5">
-        <v>0.256</v>
-      </c>
-      <c r="F5">
-        <v>0.244</v>
+        <v>0.435</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,34 +975,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.002014458699541319</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.001494293307640979</v>
       </c>
       <c r="K5">
-        <v>926.9</v>
+        <v>173.8</v>
       </c>
       <c r="L5">
-        <v>0.4764572838490799</v>
+        <v>0.255513084386945</v>
       </c>
       <c r="M5">
-        <v>131</v>
+        <v>0.001</v>
       </c>
       <c r="N5">
-        <v>0.007983618346476849</v>
+        <v>5.613247263541959e-07</v>
       </c>
       <c r="O5">
-        <v>0.1413313194519366</v>
+        <v>5.753739930955121e-06</v>
       </c>
       <c r="P5">
-        <v>131</v>
+        <v>0.001</v>
       </c>
       <c r="Q5">
-        <v>0.007983618346476849</v>
+        <v>5.613247263541959e-07</v>
       </c>
       <c r="R5">
-        <v>0.1413313194519366</v>
+        <v>5.753739930955121e-06</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1011,61 +1011,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>8206.6</v>
+        <v>1165.7</v>
       </c>
       <c r="V5">
-        <v>0.5001401703984497</v>
+        <v>0.6543362335110862</v>
       </c>
       <c r="W5">
-        <v>0.2298973163351357</v>
+        <v>0.1186753158074428</v>
       </c>
       <c r="X5">
-        <v>0.06243431710770603</v>
+        <v>0.121523332590991</v>
       </c>
       <c r="Y5">
-        <v>0.1674629992274296</v>
+        <v>-0.00284801678354818</v>
       </c>
       <c r="Z5">
-        <v>-0.979852926362446</v>
+        <v>0.408442957652867</v>
       </c>
       <c r="AA5">
-        <v>-0</v>
+        <v>0.0006103335781737667</v>
       </c>
       <c r="AB5">
-        <v>0.0621954126362939</v>
+        <v>0.09943501566563506</v>
       </c>
       <c r="AC5">
-        <v>-0.0621954126362939</v>
+        <v>-0.0988246820874613</v>
       </c>
       <c r="AD5">
-        <v>1220</v>
+        <v>1426.8</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>87.64882596285996</v>
       </c>
       <c r="AF5">
-        <v>1220</v>
+        <v>1514.44882596286</v>
       </c>
       <c r="AG5">
-        <v>-6986.6</v>
+        <v>348.7488259628599</v>
       </c>
       <c r="AH5">
-        <v>0.06920572251908831</v>
+        <v>0.4594879671775358</v>
       </c>
       <c r="AI5">
-        <v>0.2024963484265038</v>
+        <v>0.4944898720102966</v>
       </c>
       <c r="AJ5">
-        <v>-0.7415198471662069</v>
+        <v>0.1637127183042701</v>
       </c>
       <c r="AK5">
-        <v>3.202218351819599</v>
+        <v>0.1838472504843881</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>75.49206349206349</v>
+      </c>
+      <c r="AP5">
+        <v>18.45231883401375</v>
       </c>
     </row>
     <row r="6">
@@ -1076,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Asia Commercial Joint Stock Bank (HOSE:ACB)</t>
+          <t>Ho Chi Minh City Development Joint Stock Commercial Bank (HOSE:HDB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1085,10 +1091,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.277</v>
+        <v>0.228</v>
       </c>
       <c r="E6">
-        <v>0.527</v>
+        <v>0.339</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1103,10 +1109,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>426.6</v>
+        <v>315.2</v>
       </c>
       <c r="L6">
-        <v>0.4823063877897117</v>
+        <v>0.4266377910124526</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1130,55 +1136,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1254.2</v>
+        <v>2111.3</v>
       </c>
       <c r="V6">
-        <v>0.3057831090306222</v>
+        <v>1.254933428435568</v>
       </c>
       <c r="W6">
-        <v>0.3004648542048176</v>
+        <v>0.2603667602841566</v>
       </c>
       <c r="X6">
-        <v>0.0740348055035062</v>
+        <v>0.1631775169105372</v>
       </c>
       <c r="Y6">
-        <v>0.2264300487013114</v>
+        <v>0.09718924337361942</v>
       </c>
       <c r="Z6">
-        <v>0.6365141047783535</v>
+        <v>0.5753566970102167</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06523594893908483</v>
+        <v>0.1002696906275831</v>
       </c>
       <c r="AC6">
-        <v>-0.06523594893908483</v>
+        <v>-0.1002696906275831</v>
       </c>
       <c r="AD6">
-        <v>1636.2</v>
+        <v>3209.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1636.2</v>
+        <v>3209.3</v>
       </c>
       <c r="AG6">
-        <v>382</v>
+        <v>1098</v>
       </c>
       <c r="AH6">
-        <v>0.2851615601798599</v>
+        <v>0.6560704867428501</v>
       </c>
       <c r="AI6">
-        <v>0.4674990714020401</v>
+        <v>0.6732608878073341</v>
       </c>
       <c r="AJ6">
-        <v>0.08519939334463376</v>
+        <v>0.3949072075960293</v>
       </c>
       <c r="AK6">
-        <v>0.1701028632497662</v>
+        <v>0.4134814535868951</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1195,7 +1201,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Joint Stock Commercial Bank for Investment and Development of Vietnam (HOSE:BID)</t>
+          <t>Vietnam Prosperity Joint Stock Commercial Bank (HOSE:VPB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1204,10 +1210,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.09329999999999999</v>
+        <v>0.182</v>
       </c>
       <c r="E7">
-        <v>0.0888</v>
+        <v>0.264</v>
+      </c>
+      <c r="F7">
+        <v>0.241</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1222,85 +1231,82 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>432.1</v>
+        <v>765</v>
       </c>
       <c r="L7">
-        <v>0.3055869872701556</v>
+        <v>0.5158810439004653</v>
       </c>
       <c r="M7">
-        <v>143.9</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.01742637085836078</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.333024762786392</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>143.9</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.01742637085836078</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.333024762786392</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>501.9</v>
+        <v>1441.1</v>
       </c>
       <c r="V7">
-        <v>0.06078037202092617</v>
+        <v>0.2881162781398696</v>
       </c>
       <c r="W7">
-        <v>0.1280410110528343</v>
+        <v>0.2798098024871982</v>
       </c>
       <c r="X7">
-        <v>0.0788491879836343</v>
+        <v>0.1280375654873507</v>
       </c>
       <c r="Y7">
-        <v>0.04919182306920003</v>
+        <v>0.1517722369998476</v>
       </c>
       <c r="Z7">
-        <v>0.4061467758150223</v>
+        <v>0.2753300284075085</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06643789571668303</v>
+        <v>0.1005351045239566</v>
       </c>
       <c r="AC7">
-        <v>-0.06643789571668303</v>
+        <v>-0.1005351045239566</v>
       </c>
       <c r="AD7">
-        <v>4406.4</v>
+        <v>5079.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>4406.4</v>
+        <v>5079.2</v>
       </c>
       <c r="AG7">
-        <v>3904.5</v>
+        <v>3638.1</v>
       </c>
       <c r="AH7">
-        <v>0.3479469361970941</v>
+        <v>0.5038389048705485</v>
       </c>
       <c r="AI7">
-        <v>0.5386862920084597</v>
+        <v>0.5420993649607769</v>
       </c>
       <c r="AJ7">
-        <v>0.3210383075291273</v>
+        <v>0.4210812625146124</v>
       </c>
       <c r="AK7">
-        <v>0.5085308674133888</v>
+        <v>0.4588693809595883</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1317,7 +1323,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vietnam Prosperity Joint Stock Commercial Bank (HOSE:VPB)</t>
+          <t>Tien Phong Commercial Joint Stock Bank (HOSE:TPB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1326,13 +1332,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.195</v>
+        <v>0.368</v>
       </c>
       <c r="E8">
-        <v>0.315</v>
-      </c>
-      <c r="F8">
-        <v>0.213</v>
+        <v>0.452</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1347,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>538.5</v>
+        <v>253.8</v>
       </c>
       <c r="L8">
-        <v>0.4710461861441567</v>
+        <v>0.4561466570812366</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1374,55 +1377,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1632.7</v>
+        <v>1417.3</v>
       </c>
       <c r="V8">
-        <v>0.2300419872065827</v>
+        <v>1.013515446224256</v>
       </c>
       <c r="W8">
-        <v>0.2510840677017765</v>
+        <v>0.2336586264039772</v>
       </c>
       <c r="X8">
-        <v>0.08135353647191539</v>
+        <v>0.1681337060545707</v>
       </c>
       <c r="Y8">
-        <v>0.1697305312298611</v>
+        <v>0.06552492034940649</v>
       </c>
       <c r="Z8">
-        <v>0.2019930737154569</v>
+        <v>0.250687091687317</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06698329204811092</v>
+        <v>0.1005356670610681</v>
       </c>
       <c r="AC8">
-        <v>-0.06698329204811092</v>
+        <v>-0.1005356670610681</v>
       </c>
       <c r="AD8">
-        <v>4284.6</v>
+        <v>2843.5</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>4284.6</v>
+        <v>2843.5</v>
       </c>
       <c r="AG8">
-        <v>2651.900000000001</v>
+        <v>1426.2</v>
       </c>
       <c r="AH8">
-        <v>0.3764364786505008</v>
+        <v>0.6703364058558665</v>
       </c>
       <c r="AI8">
-        <v>0.6104636252244038</v>
+        <v>0.688915808600848</v>
       </c>
       <c r="AJ8">
-        <v>0.272009272460587</v>
+        <v>0.5049210507682503</v>
       </c>
       <c r="AK8">
-        <v>0.492378246903953</v>
+        <v>0.5262342262563648</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1439,7 +1442,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vietnam International Commercial Joint Stock Bank (HOSE:VIB)</t>
+          <t>Vietnam Joint Stock Commercial Bank for Industry and Trade (HOSE:CTG)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1448,10 +1451,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.352</v>
+        <v>0.103</v>
       </c>
       <c r="E9">
-        <v>0.591</v>
+        <v>0.16</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1466,82 +1469,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>225.2</v>
+        <v>652.3</v>
       </c>
       <c r="L9">
-        <v>0.4610974610974611</v>
+        <v>0.4072039453149385</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>160.2</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.02912621359223301</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.2455925187797026</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>160.2</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.02912621359223301</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.2455925187797026</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>569.2</v>
+        <v>8078.3</v>
       </c>
       <c r="V9">
-        <v>0.1760920678133894</v>
+        <v>1.468728409876005</v>
       </c>
       <c r="W9">
-        <v>0.3730329633924134</v>
+        <v>0.1565657777884454</v>
       </c>
       <c r="X9">
-        <v>0.08031134293908736</v>
+        <v>0.1425869830751515</v>
       </c>
       <c r="Y9">
-        <v>0.2927216204533261</v>
+        <v>0.01397879471329386</v>
       </c>
       <c r="Z9">
-        <v>0.4414316702819956</v>
+        <v>0.2105242407117793</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06811021291753871</v>
+        <v>0.1024412031985032</v>
       </c>
       <c r="AC9">
-        <v>-0.06811021291753871</v>
+        <v>-0.1024412031985032</v>
       </c>
       <c r="AD9">
-        <v>1857.1</v>
+        <v>7616.9</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1857.1</v>
+        <v>7616.9</v>
       </c>
       <c r="AG9">
-        <v>1287.9</v>
+        <v>-461.4000000000005</v>
       </c>
       <c r="AH9">
-        <v>0.3648884959229787</v>
+        <v>0.5806847550144468</v>
       </c>
       <c r="AI9">
-        <v>0.6905000929540807</v>
+        <v>0.6313743368700265</v>
       </c>
       <c r="AJ9">
-        <v>0.2849147180496869</v>
+        <v>-0.09156942129078365</v>
       </c>
       <c r="AK9">
-        <v>0.6074140451822856</v>
+        <v>-0.1157638557844295</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1558,7 +1564,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tien Phong Commercial Joint Stock Bank (HOSE:TPB)</t>
+          <t>Vietnam International Commercial Joint Stock Bank (HOSE:VIB)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1567,10 +1573,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.436</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="E10">
-        <v>0.5920000000000001</v>
+        <v>0.634</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1585,10 +1591,10 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>202</v>
+        <v>311.8</v>
       </c>
       <c r="L10">
-        <v>0.4500891265597148</v>
+        <v>0.4970508528614698</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1612,55 +1618,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>1304.9</v>
+        <v>1810.2</v>
       </c>
       <c r="V10">
-        <v>0.4567378368918446</v>
+        <v>1.076282775432547</v>
       </c>
       <c r="W10">
-        <v>0.3033488511788557</v>
+        <v>0.34154891006682</v>
       </c>
       <c r="X10">
-        <v>0.09027915054411383</v>
+        <v>0.1633965833351572</v>
       </c>
       <c r="Y10">
-        <v>0.2130697006347418</v>
+        <v>0.1781523267316629</v>
       </c>
       <c r="Z10">
-        <v>0.3276390713972843</v>
+        <v>0.2196736237568286</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.06859171583537452</v>
+        <v>0.1043273710805501</v>
       </c>
       <c r="AC10">
-        <v>-0.06859171583537452</v>
+        <v>-0.1043273710805501</v>
       </c>
       <c r="AD10">
-        <v>2438.2</v>
+        <v>3217.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>2438.2</v>
+        <v>3217.7</v>
       </c>
       <c r="AG10">
-        <v>1133.3</v>
+        <v>1407.5</v>
       </c>
       <c r="AH10">
-        <v>0.4604547514730322</v>
+        <v>0.6567270797616132</v>
       </c>
       <c r="AI10">
-        <v>0.6918056974236749</v>
+        <v>0.7263267194871447</v>
       </c>
       <c r="AJ10">
-        <v>0.2840137333032604</v>
+        <v>0.4555900822166116</v>
       </c>
       <c r="AK10">
-        <v>0.5106104978598782</v>
+        <v>0.5372342455818925</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1677,7 +1683,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Military Commercial Joint Stock Bank (HOSE:MBB)</t>
+          <t>Saigon - Hanoi Commercial Joint Stock Bank (HOSE:SHB)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1686,10 +1692,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.291</v>
+        <v>0.275</v>
       </c>
       <c r="E11">
-        <v>0.326</v>
+        <v>0.433</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1698,88 +1704,91 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>-0.005702473732156346</v>
+        <v>-0.0009420177153674272</v>
       </c>
       <c r="J11">
-        <v>-0.004553696264169056</v>
+        <v>-0.0007534824829581494</v>
       </c>
       <c r="K11">
-        <v>487</v>
+        <v>343.3</v>
       </c>
       <c r="L11">
-        <v>0.4175240054869684</v>
+        <v>0.5567628932857607</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>0.014</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>1.092384519350812e-05</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>4.078065831634139e-05</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>0.014</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>1.092384519350812e-05</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>4.078065831634139e-05</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
       <c r="U11">
-        <v>2027.2</v>
+        <v>1797.8</v>
       </c>
       <c r="V11">
-        <v>0.4219377666770736</v>
+        <v>1.402777777777778</v>
       </c>
       <c r="W11">
-        <v>0.2447113210391438</v>
+        <v>0.2728501033222063</v>
       </c>
       <c r="X11">
-        <v>0.08830877850011586</v>
+        <v>0.1600059302057805</v>
       </c>
       <c r="Y11">
-        <v>0.1564025425390279</v>
+        <v>0.1128441731164259</v>
       </c>
       <c r="Z11">
-        <v>0.3372846270959766</v>
+        <v>0.4861034637720379</v>
       </c>
       <c r="AA11">
-        <v>-0.001535891746368602</v>
+        <v>-0.000366270444857512</v>
       </c>
       <c r="AB11">
-        <v>0.06827507161114704</v>
+        <v>0.1040681173620591</v>
       </c>
       <c r="AC11">
-        <v>-0.06981096335751565</v>
+        <v>-0.1044343878069167</v>
       </c>
       <c r="AD11">
-        <v>3790</v>
+        <v>2319.7</v>
       </c>
       <c r="AE11">
-        <v>45.35682680593581</v>
+        <v>21.85424061647778</v>
       </c>
       <c r="AF11">
-        <v>3835.356826805936</v>
+        <v>2341.554240616478</v>
       </c>
       <c r="AG11">
-        <v>1808.156826805936</v>
+        <v>543.7542406164778</v>
       </c>
       <c r="AH11">
-        <v>0.4439143962324</v>
+        <v>0.6462750645189379</v>
       </c>
       <c r="AI11">
-        <v>0.5976909195935792</v>
+        <v>0.5691459541063809</v>
       </c>
       <c r="AJ11">
-        <v>0.2734387817429378</v>
+        <v>0.2978897073878851</v>
       </c>
       <c r="AK11">
-        <v>0.4119036425353844</v>
+        <v>0.234745718544225</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1788,10 +1797,10 @@
         <v>0</v>
       </c>
       <c r="AN11">
-        <v>1566.115702479339</v>
+        <v>612.0580474934036</v>
       </c>
       <c r="AP11">
-        <v>747.1722424817916</v>
+        <v>143.4707758882527</v>
       </c>
     </row>
     <row r="12">
@@ -1802,7 +1811,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vietnam Joint Stock Commercial Bank for Industry and Trade (HOSE:CTG)</t>
+          <t>Military Commercial Joint Stock Bank (HOSE:MBB)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1811,10 +1820,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.133</v>
+        <v>0.307</v>
       </c>
       <c r="E12">
-        <v>0.208</v>
+        <v>0.354</v>
+      </c>
+      <c r="F12">
+        <v>0.22</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1823,97 +1835,100 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>-0.002409985915080317</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>-0.001926981423426811</v>
       </c>
       <c r="K12">
-        <v>725.7</v>
+        <v>736.6</v>
       </c>
       <c r="L12">
-        <v>0.4386219401631913</v>
+        <v>0.4595134123518403</v>
       </c>
       <c r="M12">
-        <v>81.7</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>0.01139740245246432</v>
+        <v>-0</v>
       </c>
       <c r="O12">
-        <v>0.1125809563180378</v>
+        <v>-0</v>
       </c>
       <c r="P12">
-        <v>81.7</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.01139740245246432</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>0.1125809563180378</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
-        <v>4587.8</v>
+        <v>1495.6</v>
       </c>
       <c r="V12">
-        <v>0.6400122762719195</v>
+        <v>0.4592942910665478</v>
       </c>
       <c r="W12">
-        <v>0.2033228734730472</v>
+        <v>0.2992362690932727</v>
       </c>
       <c r="X12">
-        <v>0.09981787559726067</v>
+        <v>0.1587608905807731</v>
       </c>
       <c r="Y12">
-        <v>0.1035049978757865</v>
+        <v>0.1404753785124996</v>
       </c>
       <c r="Z12">
-        <v>1.729563035751621</v>
+        <v>0.3759252112966237</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>-0.0007244008987663927</v>
       </c>
       <c r="AB12">
-        <v>0.06989181364754507</v>
+        <v>0.1039689122838886</v>
       </c>
       <c r="AC12">
-        <v>-0.06989181364754507</v>
+        <v>-0.104693313182655</v>
       </c>
       <c r="AD12">
-        <v>8030.6</v>
+        <v>5805.1</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>41.41603710936874</v>
       </c>
       <c r="AF12">
-        <v>8030.6</v>
+        <v>5846.516037109369</v>
       </c>
       <c r="AG12">
-        <v>3442.8</v>
+        <v>4350.916037109369</v>
       </c>
       <c r="AH12">
-        <v>0.5283671844672969</v>
+        <v>0.6422755346559712</v>
       </c>
       <c r="AI12">
-        <v>0.6569266636672256</v>
+        <v>0.6475969928583925</v>
       </c>
       <c r="AJ12">
-        <v>0.3244526957619851</v>
+        <v>0.5719459018759054</v>
       </c>
       <c r="AK12">
-        <v>0.4508229994631189</v>
+        <v>0.5776255607329772</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
         <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>1313.371040723982</v>
+      </c>
+      <c r="AP12">
+        <v>984.3701441423913</v>
       </c>
     </row>
     <row r="13">
@@ -1924,7 +1939,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Saigon - Hanoi Commercial Joint Stock Bank (HOSE:SHB)</t>
+          <t>Vietnam Technological and Commercial Joint Stock Bank (HOSE:TCB)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1933,10 +1948,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.24</v>
+        <v>0.316</v>
       </c>
       <c r="E13">
-        <v>0.399</v>
+        <v>0.349</v>
+      </c>
+      <c r="F13">
+        <v>0.197</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1945,472 +1963,94 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>-0.006346654342222926</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>-0.005068719556408502</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>200.3</v>
+        <v>889.1</v>
       </c>
       <c r="L13">
-        <v>0.4536806342015856</v>
+        <v>0.5335453672587613</v>
       </c>
       <c r="M13">
-        <v>2.157</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.0008245097664462368</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>0.01076884672990514</v>
+        <v>-0</v>
       </c>
       <c r="P13">
-        <v>0.037</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>1.414319024502122e-05</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>0.0001847229156265602</v>
+        <v>-0</v>
       </c>
       <c r="S13">
-        <v>2.12</v>
-      </c>
-      <c r="T13">
-        <v>0.9828465461288828</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>2114.7</v>
+        <v>3304.8</v>
       </c>
       <c r="V13">
-        <v>0.8083406597607125</v>
+        <v>0.8654254065519681</v>
       </c>
       <c r="W13">
-        <v>0.1945037871431346</v>
+        <v>0.2312774757433083</v>
       </c>
       <c r="X13">
-        <v>0.08883024489637739</v>
+        <v>0.1544958509315746</v>
       </c>
       <c r="Y13">
-        <v>0.1056735422467572</v>
+        <v>0.07678162481173362</v>
       </c>
       <c r="Z13">
-        <v>0.208494658981929</v>
+        <v>0.2990452946665709</v>
       </c>
       <c r="AA13">
-        <v>-0.001056800955388425</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.07001721425180513</v>
+        <v>0.1147622008986222</v>
       </c>
       <c r="AC13">
-        <v>-0.07107401520719356</v>
+        <v>-0.1147622008986222</v>
       </c>
       <c r="AD13">
-        <v>2103.1</v>
+        <v>6442.8</v>
       </c>
       <c r="AE13">
-        <v>23.46023946045711</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>2126.560239460457</v>
+        <v>6442.8</v>
       </c>
       <c r="AG13">
-        <v>11.86023946045725</v>
+        <v>3138</v>
       </c>
       <c r="AH13">
-        <v>0.4483897500746085</v>
+        <v>0.6278614237684549</v>
       </c>
       <c r="AI13">
-        <v>0.6282750000039702</v>
+        <v>0.5831221490116574</v>
       </c>
       <c r="AJ13">
-        <v>0.004513096995292539</v>
+        <v>0.4510759411790073</v>
       </c>
       <c r="AK13">
-        <v>0.009338328287086349</v>
+        <v>0.4052169421487603</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
         <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>1112.751322751323</v>
-      </c>
-      <c r="AP13">
-        <v>6.275258973786905</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Vietnam Technological and Commercial Joint Stock Bank (HOSE:TCB)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>0.343</v>
-      </c>
-      <c r="E14">
-        <v>0.461</v>
-      </c>
-      <c r="F14">
-        <v>0.263</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>763.3</v>
-      </c>
-      <c r="L14">
-        <v>0.5371569317382124</v>
-      </c>
-      <c r="M14">
-        <v>-0</v>
-      </c>
-      <c r="N14">
-        <v>-0</v>
-      </c>
-      <c r="O14">
-        <v>-0</v>
-      </c>
-      <c r="P14">
-        <v>-0</v>
-      </c>
-      <c r="Q14">
-        <v>-0</v>
-      </c>
-      <c r="R14">
-        <v>-0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>2363.7</v>
-      </c>
-      <c r="V14">
-        <v>0.3060201967892284</v>
-      </c>
-      <c r="W14">
-        <v>0.2522722014740391</v>
-      </c>
-      <c r="X14">
-        <v>0.07871100801283286</v>
-      </c>
-      <c r="Y14">
-        <v>0.1735611934612062</v>
-      </c>
-      <c r="Z14">
-        <v>0.3572506033789219</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0.07187895000951358</v>
-      </c>
-      <c r="AC14">
-        <v>-0.07187895000951358</v>
-      </c>
-      <c r="AD14">
-        <v>4091.8</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>4091.8</v>
-      </c>
-      <c r="AG14">
-        <v>1728.1</v>
-      </c>
-      <c r="AH14">
-        <v>0.3462990233416274</v>
-      </c>
-      <c r="AI14">
-        <v>0.5134582324227328</v>
-      </c>
-      <c r="AJ14">
-        <v>0.1828270966240307</v>
-      </c>
-      <c r="AK14">
-        <v>0.3082920041388661</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Lien Viet Post Joint Stock Commercial Bank (HOSE:LPB)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>0.289</v>
-      </c>
-      <c r="E15">
-        <v>0.397</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>80.2</v>
-      </c>
-      <c r="L15">
-        <v>0.2633825944170772</v>
-      </c>
-      <c r="M15">
-        <v>-0</v>
-      </c>
-      <c r="N15">
-        <v>-0</v>
-      </c>
-      <c r="O15">
-        <v>-0</v>
-      </c>
-      <c r="P15">
-        <v>-0</v>
-      </c>
-      <c r="Q15">
-        <v>-0</v>
-      </c>
-      <c r="R15">
-        <v>-0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>733.9</v>
-      </c>
-      <c r="V15">
-        <v>0.6214225232853514</v>
-      </c>
-      <c r="W15">
-        <v>0.1479977855692932</v>
-      </c>
-      <c r="X15">
-        <v>0.1056567664539752</v>
-      </c>
-      <c r="Y15">
-        <v>0.04234101911531805</v>
-      </c>
-      <c r="Z15">
-        <v>0.1953388118011586</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0.07261426654730035</v>
-      </c>
-      <c r="AC15">
-        <v>-0.07261426654730035</v>
-      </c>
-      <c r="AD15">
-        <v>1516</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>1516</v>
-      </c>
-      <c r="AG15">
-        <v>782.1</v>
-      </c>
-      <c r="AH15">
-        <v>0.5621060437523174</v>
-      </c>
-      <c r="AI15">
-        <v>0.7121048428766029</v>
-      </c>
-      <c r="AJ15">
-        <v>0.3984004890224645</v>
-      </c>
-      <c r="AK15">
-        <v>0.5606451612903226</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Ho Chi Minh City Development Joint Stock Commercial Bank (HOSE:HDB)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>0.292</v>
-      </c>
-      <c r="E16">
-        <v>0.5820000000000001</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>-0.01140457829384121</v>
-      </c>
-      <c r="J16">
-        <v>-0.009116750769440332</v>
-      </c>
-      <c r="K16">
-        <v>245.9</v>
-      </c>
-      <c r="L16">
-        <v>0.3973820297349709</v>
-      </c>
-      <c r="M16">
-        <v>0.001</v>
-      </c>
-      <c r="N16">
-        <v>3.704938683264792e-07</v>
-      </c>
-      <c r="O16">
-        <v>4.06669377795852e-06</v>
-      </c>
-      <c r="P16">
-        <v>-0</v>
-      </c>
-      <c r="Q16">
-        <v>-0</v>
-      </c>
-      <c r="R16">
-        <v>-0</v>
-      </c>
-      <c r="S16">
-        <v>0.001</v>
-      </c>
-      <c r="T16">
-        <v>1</v>
-      </c>
-      <c r="U16">
-        <v>2373.9</v>
-      </c>
-      <c r="V16">
-        <v>0.879515394020229</v>
-      </c>
-      <c r="W16">
-        <v>0.2595524593624657</v>
-      </c>
-      <c r="X16">
-        <v>0.09275460717866341</v>
-      </c>
-      <c r="Y16">
-        <v>0.1667978521838023</v>
-      </c>
-      <c r="Z16">
-        <v>0.6606736511060943</v>
-      </c>
-      <c r="AA16">
-        <v>-0.006023197017070439</v>
-      </c>
-      <c r="AB16">
-        <v>0.06896379183269442</v>
-      </c>
-      <c r="AC16">
-        <v>-0.07498698884976486</v>
-      </c>
-      <c r="AD16">
-        <v>2447.9</v>
-      </c>
-      <c r="AE16">
-        <v>42.48576524114468</v>
-      </c>
-      <c r="AF16">
-        <v>2490.385765241145</v>
-      </c>
-      <c r="AG16">
-        <v>116.4857652411447</v>
-      </c>
-      <c r="AH16">
-        <v>0.4798906631407672</v>
-      </c>
-      <c r="AI16">
-        <v>0.6597947164551139</v>
-      </c>
-      <c r="AJ16">
-        <v>0.04137176948370035</v>
-      </c>
-      <c r="AK16">
-        <v>0.0831693196746783</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>1699.930555555556</v>
-      </c>
-      <c r="AP16">
-        <v>80.8928925285727</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/vietnam/vietnam_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.275</v>
+        <v>0.196</v>
       </c>
       <c r="E2">
-        <v>0.354</v>
-      </c>
-      <c r="F2">
-        <v>0.215</v>
+        <v>0.279</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.0002477988421735095</v>
+        <v>0.001152740254530051</v>
       </c>
       <c r="J2">
-        <v>-0.0001970528828321283</v>
+        <v>0.0009219117277284338</v>
       </c>
       <c r="K2">
-        <v>5674.7</v>
+        <v>5252</v>
       </c>
       <c r="L2">
-        <v>0.4574710790438953</v>
+        <v>0.4488927255788511</v>
       </c>
       <c r="M2">
-        <v>197.815</v>
+        <v>956.7144999999999</v>
       </c>
       <c r="N2">
-        <v>0.005388542180260036</v>
+        <v>0.02442342744817727</v>
       </c>
       <c r="O2">
-        <v>0.03485911149488079</v>
+        <v>0.1821619383092155</v>
       </c>
       <c r="P2">
-        <v>197.815</v>
+        <v>956.7144999999999</v>
       </c>
       <c r="Q2">
-        <v>0.005388542180260036</v>
+        <v>0.02442342744817727</v>
       </c>
       <c r="R2">
-        <v>0.03485911149488079</v>
+        <v>0.1821619383092155</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>35676.4</v>
+        <v>36674.9</v>
       </c>
       <c r="V2">
-        <v>0.9718362421445752</v>
+        <v>0.9362529357704483</v>
       </c>
       <c r="W2">
-        <v>0.2603667602841566</v>
+        <v>0.17601246105919</v>
       </c>
       <c r="X2">
-        <v>0.1544958509315746</v>
+        <v>0.1001902812155824</v>
       </c>
       <c r="Y2">
-        <v>0.105870909352582</v>
+        <v>0.07582217984360759</v>
       </c>
       <c r="Z2">
-        <v>0.2959913300587182</v>
+        <v>0.2850141971268249</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1005356670610681</v>
+        <v>0.08230919117318639</v>
       </c>
       <c r="AC2">
-        <v>-0.1005356670610681</v>
+        <v>-0.08181096912339703</v>
       </c>
       <c r="AD2">
-        <v>44255.4</v>
+        <v>37276.99</v>
       </c>
       <c r="AE2">
-        <v>150.9191036887065</v>
+        <v>225.8652714801192</v>
       </c>
       <c r="AF2">
-        <v>44406.31910368871</v>
+        <v>37502.85527148012</v>
       </c>
       <c r="AG2">
-        <v>8729.919103688706</v>
+        <v>827.9552714801175</v>
       </c>
       <c r="AH2">
-        <v>0.5474379922926221</v>
+        <v>0.4891154360669479</v>
       </c>
       <c r="AI2">
-        <v>0.5930986978166091</v>
+        <v>0.5330634455232368</v>
       </c>
       <c r="AJ2">
-        <v>0.1921187722217659</v>
+        <v>0.02069890493278746</v>
       </c>
       <c r="AK2">
-        <v>0.2227286141131869</v>
+        <v>0.02458404954743566</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>1632.43821468093</v>
+        <v>635.4754517558814</v>
       </c>
       <c r="AP2">
-        <v>322.0184103168095</v>
+        <v>14.11447786362287</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Joint Stock Commercial Bank for Investment and Development of Vietnam (HOSE:BID)</t>
+          <t>Vietnam Export Import Commercial Joint Stock Bank (HOSE:EIB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.132</v>
+        <v>0.0673</v>
       </c>
       <c r="E3">
-        <v>0.232</v>
+        <v>0.0542</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,97 +728,91 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.01721938640755776</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.01356283198081743</v>
       </c>
       <c r="K3">
-        <v>678.6</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L3">
-        <v>0.3881928951432985</v>
+        <v>0.3068469991546914</v>
       </c>
       <c r="M3">
-        <v>37.6</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.004584862637027644</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.05540819333922782</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>37.6</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.004584862637027644</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.05540819333922782</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>10304.6</v>
+        <v>1777.8</v>
       </c>
       <c r="V3">
-        <v>1.256520625784975</v>
+        <v>1.358239743295897</v>
       </c>
       <c r="W3">
-        <v>0.1867569352708058</v>
+        <v>0.08608015176665876</v>
       </c>
       <c r="X3">
-        <v>0.1089272133223186</v>
+        <v>0.07474933445417384</v>
       </c>
       <c r="Y3">
-        <v>0.07782972194848727</v>
-      </c>
-      <c r="Z3">
-        <v>0.2319019381541768</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
+        <v>0.01133081731248492</v>
       </c>
       <c r="AB3">
-        <v>0.09449878117410376</v>
-      </c>
-      <c r="AC3">
-        <v>-0.09449878117410376</v>
+        <v>0.07488686122534474</v>
       </c>
       <c r="AD3">
-        <v>4349.1</v>
+        <v>0.89</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>23.12946587985917</v>
       </c>
       <c r="AF3">
-        <v>4349.1</v>
+        <v>24.01946587985917</v>
       </c>
       <c r="AG3">
-        <v>-5955.5</v>
+        <v>-1753.780534120141</v>
       </c>
       <c r="AH3">
-        <v>0.3465418326693228</v>
+        <v>0.01802019288840075</v>
       </c>
       <c r="AI3">
-        <v>0.5069471966429654</v>
+        <v>0.02624162030332245</v>
       </c>
       <c r="AJ3">
-        <v>-2.652311392179568</v>
+        <v>3.942138168820238</v>
       </c>
       <c r="AK3">
-        <v>3.451263328697264</v>
+        <v>2.033414627623172</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0.1022988505747126</v>
+      </c>
+      <c r="AP3">
+        <v>-201.5839694390967</v>
       </c>
     </row>
     <row r="4">
@@ -841,13 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.283</v>
+        <v>0.197</v>
       </c>
       <c r="E4">
-        <v>0.482</v>
-      </c>
-      <c r="F4">
-        <v>0.21</v>
+        <v>0.279</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,82 +850,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>555.2</v>
+        <v>613.9</v>
       </c>
       <c r="L4">
-        <v>0.5126973866469665</v>
+        <v>0.4879968203497615</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>139.1</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.03654755648975302</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.226584134223815</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>139.1</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.03654755648975302</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.226584134223815</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>2749.7</v>
+        <v>4130.7</v>
       </c>
       <c r="V4">
-        <v>0.8851155604197515</v>
+        <v>1.085312664214398</v>
       </c>
       <c r="W4">
-        <v>0.2979020228577561</v>
+        <v>0.2628109080011987</v>
       </c>
       <c r="X4">
-        <v>0.1127032840423185</v>
+        <v>0.09131640149077103</v>
       </c>
       <c r="Y4">
-        <v>0.1851987388154376</v>
+        <v>0.1714945065104276</v>
       </c>
       <c r="Z4">
-        <v>0.48221044663134</v>
+        <v>0.821416911524649</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0952169777896979</v>
+        <v>0.08038703191172089</v>
       </c>
       <c r="AC4">
-        <v>-0.0952169777896979</v>
+        <v>-0.08038703191172089</v>
       </c>
       <c r="AD4">
-        <v>1945.3</v>
+        <v>2294.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1945.3</v>
+        <v>2294.5</v>
       </c>
       <c r="AG4">
-        <v>-804.3999999999999</v>
+        <v>-1836.2</v>
       </c>
       <c r="AH4">
-        <v>0.3850630455868089</v>
+        <v>0.3761167117449389</v>
       </c>
       <c r="AI4">
-        <v>0.4543819489862655</v>
+        <v>0.454698585073917</v>
       </c>
       <c r="AJ4">
-        <v>-0.3494049170358787</v>
+        <v>-0.9321758554167934</v>
       </c>
       <c r="AK4">
-        <v>-0.5252366960496244</v>
+        <v>-2.005679956308028</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Saigon Thuong Tin Commercial Joint Stock Bank (HOSE:STB)</t>
+          <t>Vietnam Prosperity Joint Stock Commercial Bank (HOSE:VPB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.181</v>
+        <v>0.0432</v>
       </c>
       <c r="E5">
-        <v>0.435</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,34 +966,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.002014458699541319</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.001494293307640979</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>173.8</v>
+        <v>423.3</v>
       </c>
       <c r="L5">
-        <v>0.255513084386945</v>
+        <v>0.434020301445709</v>
       </c>
       <c r="M5">
-        <v>0.001</v>
+        <v>324.0517</v>
       </c>
       <c r="N5">
-        <v>5.613247263541959e-07</v>
+        <v>0.0520832717220097</v>
       </c>
       <c r="O5">
-        <v>5.753739930955121e-06</v>
+        <v>0.7655367351759981</v>
       </c>
       <c r="P5">
-        <v>0.001</v>
+        <v>324.0517</v>
       </c>
       <c r="Q5">
-        <v>5.613247263541959e-07</v>
+        <v>0.0520832717220097</v>
       </c>
       <c r="R5">
-        <v>5.753739930955121e-06</v>
+        <v>0.7655367351759981</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1011,67 +1002,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1165.7</v>
+        <v>3586</v>
       </c>
       <c r="V5">
-        <v>0.6543362335110862</v>
+        <v>0.5763605387508438</v>
       </c>
       <c r="W5">
-        <v>0.1186753158074428</v>
+        <v>0.1067887686369485</v>
       </c>
       <c r="X5">
-        <v>0.121523332590991</v>
+        <v>0.09206305315432224</v>
       </c>
       <c r="Y5">
-        <v>-0.00284801678354818</v>
+        <v>0.01472571548262622</v>
       </c>
       <c r="Z5">
-        <v>0.408442957652867</v>
+        <v>0.128341612659144</v>
       </c>
       <c r="AA5">
-        <v>0.0006103335781737667</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.09943501566563506</v>
+        <v>0.08055218939987324</v>
       </c>
       <c r="AC5">
-        <v>-0.0988246820874613</v>
+        <v>-0.08055218939987324</v>
       </c>
       <c r="AD5">
-        <v>1426.8</v>
+        <v>3914.8</v>
       </c>
       <c r="AE5">
-        <v>87.64882596285996</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1514.44882596286</v>
+        <v>3914.8</v>
       </c>
       <c r="AG5">
-        <v>348.7488259628599</v>
+        <v>328.8000000000002</v>
       </c>
       <c r="AH5">
-        <v>0.4594879671775358</v>
+        <v>0.3862044472505574</v>
       </c>
       <c r="AI5">
-        <v>0.4944898720102966</v>
+        <v>0.4636191378493605</v>
       </c>
       <c r="AJ5">
-        <v>0.1637127183042701</v>
+        <v>0.05019387537019512</v>
       </c>
       <c r="AK5">
-        <v>0.1838472504843881</v>
+        <v>0.06768217373404697</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>75.49206349206349</v>
-      </c>
-      <c r="AP5">
-        <v>18.45231883401375</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City Development Joint Stock Commercial Bank (HOSE:HDB)</t>
+          <t>Southeast Asia Commercial Joint Stock Bank (HOSE:SSB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1090,12 +1075,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.228</v>
-      </c>
-      <c r="E6">
-        <v>0.339</v>
-      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1109,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>315.2</v>
+        <v>138.1</v>
       </c>
       <c r="L6">
-        <v>0.4266377910124526</v>
+        <v>0.4316974054391998</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1136,55 +1115,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>2111.3</v>
+        <v>1712.2</v>
       </c>
       <c r="V6">
-        <v>1.254933428435568</v>
+        <v>0.7001431200163566</v>
       </c>
       <c r="W6">
-        <v>0.2603667602841566</v>
+        <v>0.1338307975579029</v>
       </c>
       <c r="X6">
-        <v>0.1631775169105372</v>
+        <v>0.09590368457074247</v>
       </c>
       <c r="Y6">
-        <v>0.09718924337361942</v>
+        <v>0.03792711298716042</v>
       </c>
       <c r="Z6">
-        <v>0.5753566970102167</v>
+        <v>1.20625942684766</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1002696906275831</v>
+        <v>0.08132381387129585</v>
       </c>
       <c r="AC6">
-        <v>-0.1002696906275831</v>
+        <v>-0.08132381387129585</v>
       </c>
       <c r="AD6">
-        <v>3209.3</v>
+        <v>1870.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>3209.3</v>
+        <v>1870.1</v>
       </c>
       <c r="AG6">
-        <v>1098</v>
+        <v>157.8999999999999</v>
       </c>
       <c r="AH6">
-        <v>0.6560704867428501</v>
+        <v>0.4333348781166002</v>
       </c>
       <c r="AI6">
-        <v>0.6732608878073341</v>
+        <v>0.613368755944767</v>
       </c>
       <c r="AJ6">
-        <v>0.3949072075960293</v>
+        <v>0.06065145578858411</v>
       </c>
       <c r="AK6">
-        <v>0.4134814535868951</v>
+        <v>0.1181267300067329</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1201,7 +1180,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vietnam Prosperity Joint Stock Commercial Bank (HOSE:VPB)</t>
+          <t>Tien Phong Commercial Joint Stock Bank (HOSE:TPB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1210,13 +1189,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.182</v>
+        <v>0.233</v>
       </c>
       <c r="E7">
-        <v>0.264</v>
-      </c>
-      <c r="F7">
-        <v>0.241</v>
+        <v>0.289</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1231,82 +1207,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>765</v>
+        <v>226</v>
       </c>
       <c r="L7">
-        <v>0.5158810439004653</v>
+        <v>0.4106850808649828</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>162.8</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.1036546542722526</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.720353982300885</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>162.8</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.1036546542722526</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.720353982300885</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>1441.1</v>
+        <v>1784.5</v>
       </c>
       <c r="V7">
-        <v>0.2881162781398696</v>
+        <v>1.136189991086209</v>
       </c>
       <c r="W7">
-        <v>0.2798098024871982</v>
+        <v>0.17601246105919</v>
       </c>
       <c r="X7">
-        <v>0.1280375654873507</v>
+        <v>0.09709916226742103</v>
       </c>
       <c r="Y7">
-        <v>0.1517722369998476</v>
+        <v>0.07891329879176899</v>
       </c>
       <c r="Z7">
-        <v>0.2753300284075085</v>
+        <v>0.2030477455538337</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.1005351045239566</v>
+        <v>0.08154037953870484</v>
       </c>
       <c r="AC7">
-        <v>-0.1005351045239566</v>
+        <v>-0.08154037953870484</v>
       </c>
       <c r="AD7">
-        <v>5079.2</v>
+        <v>1267.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>5079.2</v>
+        <v>1267.3</v>
       </c>
       <c r="AG7">
-        <v>3638.1</v>
+        <v>-517.2</v>
       </c>
       <c r="AH7">
-        <v>0.5038389048705485</v>
+        <v>0.446562599104972</v>
       </c>
       <c r="AI7">
-        <v>0.5420993649607769</v>
+        <v>0.4872731467240848</v>
       </c>
       <c r="AJ7">
-        <v>0.4210812625146124</v>
+        <v>-0.4909815834440859</v>
       </c>
       <c r="AK7">
-        <v>0.4588693809595883</v>
+        <v>-0.6335905916942302</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1323,7 +1302,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tien Phong Commercial Joint Stock Bank (HOSE:TPB)</t>
+          <t>Saigon Thuong Tin Commercial Joint Stock Bank (HOSE:STB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1332,10 +1311,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.368</v>
+        <v>0.183</v>
       </c>
       <c r="E8">
-        <v>0.452</v>
+        <v>0.4</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1344,94 +1323,103 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>0.001606555298511723</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>0.001325776392492308</v>
       </c>
       <c r="K8">
-        <v>253.8</v>
+        <v>296.9</v>
       </c>
       <c r="L8">
-        <v>0.4561466570812366</v>
+        <v>0.3464006533660016</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>0.008</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>3.703017959637104e-06</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>2.694509936005389e-05</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>0.008</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>3.703017959637104e-06</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>2.694509936005389e-05</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>1417.3</v>
+        <v>423.8</v>
       </c>
       <c r="V8">
-        <v>1.013515446224256</v>
+        <v>0.1961673764117756</v>
       </c>
       <c r="W8">
-        <v>0.2336586264039772</v>
+        <v>0.1917710890065883</v>
       </c>
       <c r="X8">
-        <v>0.1681337060545707</v>
+        <v>0.09192498804764562</v>
       </c>
       <c r="Y8">
-        <v>0.06552492034940649</v>
+        <v>0.09984610095894264</v>
       </c>
       <c r="Z8">
-        <v>0.250687091687317</v>
+        <v>0.4512441733880364</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>0.0005982488723275644</v>
       </c>
       <c r="AB8">
-        <v>0.1005356670610681</v>
+        <v>0.08230919117318639</v>
       </c>
       <c r="AC8">
-        <v>-0.1005356670610681</v>
+        <v>-0.08171094230085882</v>
       </c>
       <c r="AD8">
-        <v>2843.5</v>
+        <v>1258.7</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>90.115107268228</v>
       </c>
       <c r="AF8">
-        <v>2843.5</v>
+        <v>1348.815107268228</v>
       </c>
       <c r="AG8">
-        <v>1426.2</v>
+        <v>925.0151072682281</v>
       </c>
       <c r="AH8">
-        <v>0.6703364058558665</v>
+        <v>0.3843637582873118</v>
       </c>
       <c r="AI8">
-        <v>0.688915808600848</v>
+        <v>0.4283700053252634</v>
       </c>
       <c r="AJ8">
-        <v>0.5049210507682503</v>
+        <v>0.2998024820353006</v>
       </c>
       <c r="AK8">
-        <v>0.5262342262563648</v>
+        <v>0.3394656607102784</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
         <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>64.88144329896907</v>
+      </c>
+      <c r="AP8">
+        <v>47.68119109630042</v>
       </c>
     </row>
     <row r="9">
@@ -1442,7 +1430,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vietnam Joint Stock Commercial Bank for Industry and Trade (HOSE:CTG)</t>
+          <t>Vietnam International Commercial Joint Stock Bank (HOSE:VIB)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1451,10 +1439,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.103</v>
+        <v>0.279</v>
       </c>
       <c r="E9">
-        <v>0.16</v>
+        <v>0.347</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1463,34 +1451,34 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>0.01298477612185308</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>0.01039180134122466</v>
       </c>
       <c r="K9">
-        <v>652.3</v>
+        <v>365.6</v>
       </c>
       <c r="L9">
-        <v>0.4072039453149385</v>
+        <v>0.5074253990284525</v>
       </c>
       <c r="M9">
-        <v>160.2</v>
+        <v>130.2</v>
       </c>
       <c r="N9">
-        <v>0.02912621359223301</v>
+        <v>0.06386735995290886</v>
       </c>
       <c r="O9">
-        <v>0.2455925187797026</v>
+        <v>0.3561269146608315</v>
       </c>
       <c r="P9">
-        <v>160.2</v>
+        <v>130.2</v>
       </c>
       <c r="Q9">
-        <v>0.02912621359223301</v>
+        <v>0.06386735995290886</v>
       </c>
       <c r="R9">
-        <v>0.2455925187797026</v>
+        <v>0.3561269146608315</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1499,61 +1487,67 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>8078.3</v>
+        <v>2518.5</v>
       </c>
       <c r="V9">
-        <v>1.468728409876005</v>
+        <v>1.235406651623663</v>
       </c>
       <c r="W9">
-        <v>0.1565657777884454</v>
+        <v>0.301550643352029</v>
       </c>
       <c r="X9">
-        <v>0.1425869830751515</v>
+        <v>0.1017859568576638</v>
       </c>
       <c r="Y9">
-        <v>0.01397879471329386</v>
+        <v>0.1997646864943652</v>
       </c>
       <c r="Z9">
-        <v>0.2105242407117793</v>
+        <v>0.2676327105267595</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>0.00278118596020757</v>
       </c>
       <c r="AB9">
-        <v>0.1024412031985032</v>
+        <v>0.0845921550836046</v>
       </c>
       <c r="AC9">
-        <v>-0.1024412031985032</v>
+        <v>-0.08181096912339703</v>
       </c>
       <c r="AD9">
-        <v>7616.9</v>
+        <v>1909.8</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>72.22234402102427</v>
       </c>
       <c r="AF9">
-        <v>7616.9</v>
+        <v>1982.022344021024</v>
       </c>
       <c r="AG9">
-        <v>-461.4000000000005</v>
+        <v>-536.4776559789757</v>
       </c>
       <c r="AH9">
-        <v>0.5806847550144468</v>
+        <v>0.4929640673584886</v>
       </c>
       <c r="AI9">
-        <v>0.6313743368700265</v>
+        <v>0.5718434987703015</v>
       </c>
       <c r="AJ9">
-        <v>-0.09156942129078365</v>
+        <v>-0.3571464455703929</v>
       </c>
       <c r="AK9">
-        <v>-0.1157638557844295</v>
+        <v>-0.5661899789110112</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
         <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>80.24369747899159</v>
+      </c>
+      <c r="AP9">
+        <v>-22.5410779823099</v>
       </c>
     </row>
     <row r="10">
@@ -1564,7 +1558,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vietnam International Commercial Joint Stock Bank (HOSE:VIB)</t>
+          <t>Vietnam Joint Stock Commercial Bank for Industry and Trade (HOSE:CTG)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1573,10 +1567,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.3720000000000001</v>
+        <v>0.111</v>
       </c>
       <c r="E10">
-        <v>0.634</v>
+        <v>0.186</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1591,10 +1585,10 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>311.8</v>
+        <v>741.2</v>
       </c>
       <c r="L10">
-        <v>0.4970508528614698</v>
+        <v>0.4206583427922815</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1618,55 +1612,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>1810.2</v>
+        <v>9493.5</v>
       </c>
       <c r="V10">
-        <v>1.076282775432547</v>
+        <v>1.591107163208527</v>
       </c>
       <c r="W10">
-        <v>0.34154891006682</v>
+        <v>0.1678252009509793</v>
       </c>
       <c r="X10">
-        <v>0.1633965833351572</v>
+        <v>0.1001902812155824</v>
       </c>
       <c r="Y10">
-        <v>0.1781523267316629</v>
+        <v>0.06763491973539687</v>
       </c>
       <c r="Z10">
-        <v>0.2196736237568286</v>
+        <v>0.4455007458724179</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.1043273710805501</v>
+        <v>0.08205614644138198</v>
       </c>
       <c r="AC10">
-        <v>-0.1043273710805501</v>
+        <v>-0.08205614644138198</v>
       </c>
       <c r="AD10">
-        <v>3217.7</v>
+        <v>5465.1</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>3217.7</v>
+        <v>5465.1</v>
       </c>
       <c r="AG10">
-        <v>1407.5</v>
+        <v>-4028.4</v>
       </c>
       <c r="AH10">
-        <v>0.6567270797616132</v>
+        <v>0.4780653796023339</v>
       </c>
       <c r="AI10">
-        <v>0.7263267194871447</v>
+        <v>0.521031556869101</v>
       </c>
       <c r="AJ10">
-        <v>0.4555900822166116</v>
+        <v>-2.078423279331338</v>
       </c>
       <c r="AK10">
-        <v>0.5372342455818925</v>
+        <v>-4.046609743847313</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1683,7 +1677,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Saigon - Hanoi Commercial Joint Stock Bank (HOSE:SHB)</t>
+          <t>Ho Chi Minh City Development Joint Stock Commercial Bank (HOSE:HDB)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1692,10 +1686,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.275</v>
+        <v>0.196</v>
       </c>
       <c r="E11">
-        <v>0.433</v>
+        <v>0.25</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1704,34 +1698,34 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>-0.0009420177153674272</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>-0.0007534824829581494</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>343.3</v>
+        <v>339.2</v>
       </c>
       <c r="L11">
-        <v>0.5567628932857607</v>
+        <v>0.4140119614304895</v>
       </c>
       <c r="M11">
-        <v>0.014</v>
+        <v>106.7</v>
       </c>
       <c r="N11">
-        <v>1.092384519350812e-05</v>
+        <v>0.04435483870967742</v>
       </c>
       <c r="O11">
-        <v>4.078065831634139e-05</v>
+        <v>0.3145636792452831</v>
       </c>
       <c r="P11">
-        <v>0.014</v>
+        <v>106.7</v>
       </c>
       <c r="Q11">
-        <v>1.092384519350812e-05</v>
+        <v>0.04435483870967742</v>
       </c>
       <c r="R11">
-        <v>4.078065831634139e-05</v>
+        <v>0.3145636792452831</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1740,67 +1734,61 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>1797.8</v>
+        <v>3528</v>
       </c>
       <c r="V11">
-        <v>1.402777777777778</v>
+        <v>1.466577984702361</v>
       </c>
       <c r="W11">
-        <v>0.2728501033222063</v>
+        <v>0.2381186381186381</v>
       </c>
       <c r="X11">
-        <v>0.1600059302057805</v>
+        <v>0.1103641739327315</v>
       </c>
       <c r="Y11">
-        <v>0.1128441731164259</v>
+        <v>0.1277544641859066</v>
       </c>
       <c r="Z11">
-        <v>0.4861034637720379</v>
+        <v>0.2818398538684609</v>
       </c>
       <c r="AA11">
-        <v>-0.000366270444857512</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.1040681173620591</v>
+        <v>0.08340446976065598</v>
       </c>
       <c r="AC11">
-        <v>-0.1044343878069167</v>
+        <v>-0.08340446976065598</v>
       </c>
       <c r="AD11">
-        <v>2319.7</v>
+        <v>3066.9</v>
       </c>
       <c r="AE11">
-        <v>21.85424061647778</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>2341.554240616478</v>
+        <v>3066.9</v>
       </c>
       <c r="AG11">
-        <v>543.7542406164778</v>
+        <v>-461.0999999999999</v>
       </c>
       <c r="AH11">
-        <v>0.6462750645189379</v>
+        <v>0.5604202832343536</v>
       </c>
       <c r="AI11">
-        <v>0.5691459541063809</v>
+        <v>0.6411414236437755</v>
       </c>
       <c r="AJ11">
-        <v>0.2978897073878851</v>
+        <v>-0.2371303677037798</v>
       </c>
       <c r="AK11">
-        <v>0.234745718544225</v>
+        <v>-0.3672640382317801</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
         <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>612.0580474934036</v>
-      </c>
-      <c r="AP11">
-        <v>143.4707758882527</v>
       </c>
     </row>
     <row r="12">
@@ -1811,7 +1799,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Military Commercial Joint Stock Bank (HOSE:MBB)</t>
+          <t>Vietnam Maritime Commercial Joint Stock Bank (HOSE:MSB)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1819,15 +1807,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D12">
-        <v>0.307</v>
-      </c>
-      <c r="E12">
-        <v>0.354</v>
-      </c>
-      <c r="F12">
-        <v>0.22</v>
-      </c>
       <c r="G12">
         <v>0</v>
       </c>
@@ -1835,16 +1814,16 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>-0.002409985915080317</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>-0.001926981423426811</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>736.6</v>
+        <v>203.1</v>
       </c>
       <c r="L12">
-        <v>0.4595134123518403</v>
+        <v>0.4548712206047033</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1868,67 +1847,61 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1495.6</v>
+        <v>1866.4</v>
       </c>
       <c r="V12">
-        <v>0.4592942910665478</v>
+        <v>1.750844277673546</v>
       </c>
       <c r="W12">
-        <v>0.2992362690932727</v>
+        <v>0.1925483503981797</v>
       </c>
       <c r="X12">
-        <v>0.1587608905807731</v>
+        <v>0.1123092933779835</v>
       </c>
       <c r="Y12">
-        <v>0.1404753785124996</v>
+        <v>0.08023905702019629</v>
       </c>
       <c r="Z12">
-        <v>0.3759252112966237</v>
+        <v>0.2228255173893732</v>
       </c>
       <c r="AA12">
-        <v>-0.0007244008987663927</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.1039689122838886</v>
+        <v>0.08361521950826784</v>
       </c>
       <c r="AC12">
-        <v>-0.104693313182655</v>
+        <v>-0.08361521950826784</v>
       </c>
       <c r="AD12">
-        <v>5805.1</v>
+        <v>1432.2</v>
       </c>
       <c r="AE12">
-        <v>41.41603710936874</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>5846.516037109369</v>
+        <v>1432.2</v>
       </c>
       <c r="AG12">
-        <v>4350.916037109369</v>
+        <v>-434.2</v>
       </c>
       <c r="AH12">
-        <v>0.6422755346559712</v>
+        <v>0.5732927707949724</v>
       </c>
       <c r="AI12">
-        <v>0.6475969928583925</v>
+        <v>0.5322382845887993</v>
       </c>
       <c r="AJ12">
-        <v>0.5719459018759054</v>
+        <v>-0.6872427983539096</v>
       </c>
       <c r="AK12">
-        <v>0.5776255607329772</v>
+        <v>-0.5266221952698605</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
         <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>1313.371040723982</v>
-      </c>
-      <c r="AP12">
-        <v>984.3701441423913</v>
       </c>
     </row>
     <row r="13">
@@ -1939,117 +1912,364 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Military Commercial Joint Stock Bank (HOSE:MBB)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.234</v>
+      </c>
+      <c r="E13">
+        <v>0.319</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>773.1</v>
+      </c>
+      <c r="L13">
+        <v>0.4707995858961087</v>
+      </c>
+      <c r="M13">
+        <v>93.85379999999999</v>
+      </c>
+      <c r="N13">
+        <v>0.02354054528581103</v>
+      </c>
+      <c r="O13">
+        <v>0.1213993015133877</v>
+      </c>
+      <c r="P13">
+        <v>93.85379999999999</v>
+      </c>
+      <c r="Q13">
+        <v>0.02354054528581103</v>
+      </c>
+      <c r="R13">
+        <v>0.1213993015133877</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>715.7</v>
+      </c>
+      <c r="V13">
+        <v>0.1795129047630992</v>
+      </c>
+      <c r="W13">
+        <v>0.2661731795489757</v>
+      </c>
+      <c r="X13">
+        <v>0.1170204487185475</v>
+      </c>
+      <c r="Y13">
+        <v>0.1491527308304283</v>
+      </c>
+      <c r="Z13">
+        <v>0.2641276356869072</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.08407789987504138</v>
+      </c>
+      <c r="AC13">
+        <v>-0.08407789987504138</v>
+      </c>
+      <c r="AD13">
+        <v>6019.2</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>6019.2</v>
+      </c>
+      <c r="AG13">
+        <v>5303.5</v>
+      </c>
+      <c r="AH13">
+        <v>0.6015530526378908</v>
+      </c>
+      <c r="AI13">
+        <v>0.6225062827712451</v>
+      </c>
+      <c r="AJ13">
+        <v>0.5708580900714717</v>
+      </c>
+      <c r="AK13">
+        <v>0.5923315761258041</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Saigon - Hanoi Commercial Joint Stock Bank (HOSE:SHB)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.24</v>
+      </c>
+      <c r="E14">
+        <v>0.352</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>-0.002244719956117646</v>
+      </c>
+      <c r="J14">
+        <v>-0.001811006505810261</v>
+      </c>
+      <c r="K14">
+        <v>304.4</v>
+      </c>
+      <c r="L14">
+        <v>0.5177751318251403</v>
+      </c>
+      <c r="M14">
+        <v>0.001</v>
+      </c>
+      <c r="N14">
+        <v>6.2402496099844e-07</v>
+      </c>
+      <c r="O14">
+        <v>3.28515111695138e-06</v>
+      </c>
+      <c r="P14">
+        <v>0.001</v>
+      </c>
+      <c r="Q14">
+        <v>6.2402496099844e-07</v>
+      </c>
+      <c r="R14">
+        <v>3.28515111695138e-06</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>2276.5</v>
+      </c>
+      <c r="V14">
+        <v>1.420592823712949</v>
+      </c>
+      <c r="W14">
+        <v>0.1717251494979127</v>
+      </c>
+      <c r="X14">
+        <v>0.1083862531808168</v>
+      </c>
+      <c r="Y14">
+        <v>0.0633388963170959</v>
+      </c>
+      <c r="Z14">
+        <v>0.2517882626087507</v>
+      </c>
+      <c r="AA14">
+        <v>-0.0004559901816711099</v>
+      </c>
+      <c r="AB14">
+        <v>0.08571776336712586</v>
+      </c>
+      <c r="AC14">
+        <v>-0.08617375354879697</v>
+      </c>
+      <c r="AD14">
+        <v>1890.8</v>
+      </c>
+      <c r="AE14">
+        <v>40.39835431100781</v>
+      </c>
+      <c r="AF14">
+        <v>1931.198354311008</v>
+      </c>
+      <c r="AG14">
+        <v>-345.3016456889923</v>
+      </c>
+      <c r="AH14">
+        <v>0.5465091133075926</v>
+      </c>
+      <c r="AI14">
+        <v>0.4863868920167642</v>
+      </c>
+      <c r="AJ14">
+        <v>-0.2746596386361249</v>
+      </c>
+      <c r="AK14">
+        <v>-0.2038382415249956</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>279.7041420118343</v>
+      </c>
+      <c r="AP14">
+        <v>-51.08012510192194</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Vietnam Technological and Commercial Joint Stock Bank (HOSE:TCB)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D13">
-        <v>0.316</v>
-      </c>
-      <c r="E13">
-        <v>0.349</v>
-      </c>
-      <c r="F13">
-        <v>0.197</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>889.1</v>
-      </c>
-      <c r="L13">
-        <v>0.5335453672587613</v>
-      </c>
-      <c r="M13">
-        <v>-0</v>
-      </c>
-      <c r="N13">
-        <v>-0</v>
-      </c>
-      <c r="O13">
-        <v>-0</v>
-      </c>
-      <c r="P13">
-        <v>-0</v>
-      </c>
-      <c r="Q13">
-        <v>-0</v>
-      </c>
-      <c r="R13">
-        <v>-0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>3304.8</v>
-      </c>
-      <c r="V13">
-        <v>0.8654254065519681</v>
-      </c>
-      <c r="W13">
-        <v>0.2312774757433083</v>
-      </c>
-      <c r="X13">
-        <v>0.1544958509315746</v>
-      </c>
-      <c r="Y13">
-        <v>0.07678162481173362</v>
-      </c>
-      <c r="Z13">
-        <v>0.2990452946665709</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0.1147622008986222</v>
-      </c>
-      <c r="AC13">
-        <v>-0.1147622008986222</v>
-      </c>
-      <c r="AD13">
-        <v>6442.8</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>6442.8</v>
-      </c>
-      <c r="AG13">
-        <v>3138</v>
-      </c>
-      <c r="AH13">
-        <v>0.6278614237684549</v>
-      </c>
-      <c r="AI13">
-        <v>0.5831221490116574</v>
-      </c>
-      <c r="AJ13">
-        <v>0.4510759411790073</v>
-      </c>
-      <c r="AK13">
-        <v>0.4052169421487603</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
+      <c r="D15">
+        <v>0.181</v>
+      </c>
+      <c r="E15">
+        <v>0.162</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>754.6</v>
+      </c>
+      <c r="L15">
+        <v>0.4950144319076358</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>-0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>-0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>2861.3</v>
+      </c>
+      <c r="V15">
+        <v>0.6230239951225885</v>
+      </c>
+      <c r="W15">
+        <v>0.1698631370430398</v>
+      </c>
+      <c r="X15">
+        <v>0.116730681880856</v>
+      </c>
+      <c r="Y15">
+        <v>0.05313245516218386</v>
+      </c>
+      <c r="Z15">
+        <v>0.219822054306603</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.09388756113645669</v>
+      </c>
+      <c r="AC15">
+        <v>-0.09388756113645669</v>
+      </c>
+      <c r="AD15">
+        <v>6886.7</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>6886.7</v>
+      </c>
+      <c r="AG15">
+        <v>4025.4</v>
+      </c>
+      <c r="AH15">
+        <v>0.5999233402733617</v>
+      </c>
+      <c r="AI15">
+        <v>0.5700769020636904</v>
+      </c>
+      <c r="AJ15">
+        <v>0.4670921327454166</v>
+      </c>
+      <c r="AK15">
+        <v>0.4366417181906931</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/vietnam/vietnam_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.179</v>
+        <v>0.169</v>
       </c>
       <c r="E2">
-        <v>0.194</v>
+        <v>0.24</v>
       </c>
       <c r="F2">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,97 +603,103 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.0006972573727520479</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.000554711330558704</v>
       </c>
       <c r="K2">
-        <v>920</v>
+        <v>7047.2</v>
       </c>
       <c r="L2">
-        <v>0.5271602108640844</v>
+        <v>0.4552219523538835</v>
       </c>
       <c r="M2">
-        <v>212.2</v>
+        <v>1625.437</v>
       </c>
       <c r="N2">
-        <v>0.03124355840866928</v>
+        <v>0.02850158776917992</v>
       </c>
       <c r="O2">
-        <v>0.2306521739130435</v>
+        <v>0.2306500454081053</v>
       </c>
       <c r="P2">
-        <v>212.2</v>
+        <v>1418.337</v>
       </c>
       <c r="Q2">
-        <v>0.03124355840866928</v>
+        <v>0.02487014660782014</v>
       </c>
       <c r="R2">
-        <v>0.2306521739130435</v>
+        <v>0.2012624872289704</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>207.1</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1274118898486992</v>
       </c>
       <c r="U2">
-        <v>3359.6</v>
+        <v>46161.9</v>
       </c>
       <c r="V2">
-        <v>0.4946553196501663</v>
+        <v>0.8094361359081321</v>
       </c>
       <c r="W2">
         <v>0.1775205016883743</v>
       </c>
       <c r="X2">
-        <v>0.1095705542703871</v>
+        <v>0.108511480403794</v>
       </c>
       <c r="Y2">
-        <v>0.06794994741798718</v>
+        <v>0.06900902128458034</v>
       </c>
       <c r="Z2">
-        <v>0.1895493695083143</v>
+        <v>0.4061433564980496</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0926400152259272</v>
+        <v>0.08553419965828096</v>
       </c>
       <c r="AC2">
-        <v>-0.0926400152259272</v>
+        <v>-0.08553419965828096</v>
       </c>
       <c r="AD2">
-        <v>7985.1</v>
+        <v>60600.7</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>69.0294903195005</v>
       </c>
       <c r="AF2">
-        <v>7985.1</v>
+        <v>60669.7294903195</v>
       </c>
       <c r="AG2">
-        <v>4625.5</v>
+        <v>14507.8294903195</v>
       </c>
       <c r="AH2">
-        <v>0.5403772103756539</v>
+        <v>0.5154632418614182</v>
       </c>
       <c r="AI2">
-        <v>0.5759385480904469</v>
+        <v>0.5742459146721994</v>
       </c>
       <c r="AJ2">
-        <v>0.4051308102616206</v>
+        <v>0.2028002587408712</v>
       </c>
       <c r="AK2">
-        <v>0.4403183276375787</v>
+        <v>0.2438732122539982</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>2463.443089430894</v>
+      </c>
+      <c r="AP2">
+        <v>589.7491662731503</v>
       </c>
     </row>
     <row r="3">
@@ -704,120 +710,1801 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Vietnam International Commercial Joint Stock Bank (HOSE:VIB)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.182</v>
+      </c>
+      <c r="E3">
+        <v>0.178</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0.01634726932621521</v>
+      </c>
+      <c r="J3">
+        <v>0.01307602789734984</v>
+      </c>
+      <c r="K3">
+        <v>292.6</v>
+      </c>
+      <c r="L3">
+        <v>0.4431319097379979</v>
+      </c>
+      <c r="M3">
+        <v>129.1</v>
+      </c>
+      <c r="N3">
+        <v>0.05640263882214164</v>
+      </c>
+      <c r="O3">
+        <v>0.4412166780587833</v>
+      </c>
+      <c r="P3">
+        <v>129.1</v>
+      </c>
+      <c r="Q3">
+        <v>0.05640263882214164</v>
+      </c>
+      <c r="R3">
+        <v>0.4412166780587833</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>1670.3</v>
+      </c>
+      <c r="V3">
+        <v>0.7297391760234173</v>
+      </c>
+      <c r="W3">
+        <v>0.1971698113207547</v>
+      </c>
+      <c r="X3">
+        <v>0.1012445058452604</v>
+      </c>
+      <c r="Y3">
+        <v>0.0959253054754943</v>
+      </c>
+      <c r="Z3">
+        <v>0.6992262835894246</v>
+      </c>
+      <c r="AA3">
+        <v>0.009143102390775565</v>
+      </c>
+      <c r="AB3">
+        <v>0.08462385636247739</v>
+      </c>
+      <c r="AC3">
+        <v>-0.07548075397170183</v>
+      </c>
+      <c r="AD3">
+        <v>1897.6</v>
+      </c>
+      <c r="AE3">
+        <v>69.0294903195005</v>
+      </c>
+      <c r="AF3">
+        <v>1966.6294903195</v>
+      </c>
+      <c r="AG3">
+        <v>296.3294903195003</v>
+      </c>
+      <c r="AH3">
+        <v>0.4621350867837242</v>
+      </c>
+      <c r="AI3">
+        <v>0.5473153038562625</v>
+      </c>
+      <c r="AJ3">
+        <v>0.1146240561733952</v>
+      </c>
+      <c r="AK3">
+        <v>0.1541031492892984</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>77.13821138211381</v>
+      </c>
+      <c r="AP3">
+        <v>12.0459142406301</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Saigon Thuong Tin Commercial Joint Stock Bank (HOSE:STB)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.15</v>
+      </c>
+      <c r="E4">
+        <v>0.257</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>356.3</v>
+      </c>
+      <c r="L4">
+        <v>0.3488007831620167</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>2809.5</v>
+      </c>
+      <c r="V4">
+        <v>1.035569480280133</v>
+      </c>
+      <c r="W4">
+        <v>0.1979554419689983</v>
+      </c>
+      <c r="X4">
+        <v>0.0943058617208142</v>
+      </c>
+      <c r="Y4">
+        <v>0.1036495802481841</v>
+      </c>
+      <c r="Z4">
+        <v>0.3876954607560346</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.08347508325476985</v>
+      </c>
+      <c r="AC4">
+        <v>-0.08347508325476985</v>
+      </c>
+      <c r="AD4">
+        <v>1614.9</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>1614.9</v>
+      </c>
+      <c r="AG4">
+        <v>-1194.6</v>
+      </c>
+      <c r="AH4">
+        <v>0.3731370872709629</v>
+      </c>
+      <c r="AI4">
+        <v>0.436070531687954</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.7867492096944151</v>
+      </c>
+      <c r="AK4">
+        <v>-1.336540613112553</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh City Development Joint Stock Commercial Bank (HOSE:HDB)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.241</v>
+      </c>
+      <c r="E5">
+        <v>0.318</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>529.1</v>
+      </c>
+      <c r="L5">
+        <v>0.4622575572252316</v>
+      </c>
+      <c r="M5">
+        <v>118.6</v>
+      </c>
+      <c r="N5">
+        <v>0.03412164106105069</v>
+      </c>
+      <c r="O5">
+        <v>0.2241542241542241</v>
+      </c>
+      <c r="P5">
+        <v>118.6</v>
+      </c>
+      <c r="Q5">
+        <v>0.03412164106105069</v>
+      </c>
+      <c r="R5">
+        <v>0.2241542241542241</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>3930.2</v>
+      </c>
+      <c r="V5">
+        <v>1.130732493238966</v>
+      </c>
+      <c r="W5">
+        <v>0.3118957792973355</v>
+      </c>
+      <c r="X5">
+        <v>0.09782974832337532</v>
+      </c>
+      <c r="Y5">
+        <v>0.2140660309739602</v>
+      </c>
+      <c r="Z5">
+        <v>0.3899191954978401</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.08410232951852542</v>
+      </c>
+      <c r="AC5">
+        <v>-0.08410232951852542</v>
+      </c>
+      <c r="AD5">
+        <v>2534.9</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>2534.9</v>
+      </c>
+      <c r="AG5">
+        <v>-1395.3</v>
+      </c>
+      <c r="AH5">
+        <v>0.4217312459447319</v>
+      </c>
+      <c r="AI5">
+        <v>0.5373852578915012</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.670656092285508</v>
+      </c>
+      <c r="AK5">
+        <v>-1.773160503240564</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Southeast Asia Commercial Joint Stock Bank (HOSE:SSB)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>151.5</v>
+      </c>
+      <c r="L6">
+        <v>0.4470345234582473</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>-0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1922.9</v>
+      </c>
+      <c r="V6">
+        <v>1.038282937365011</v>
+      </c>
+      <c r="W6">
+        <v>0.136388188692834</v>
+      </c>
+      <c r="X6">
+        <v>0.1015561488429435</v>
+      </c>
+      <c r="Y6">
+        <v>0.03483203984989046</v>
+      </c>
+      <c r="Z6">
+        <v>0.3315722532041875</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.08466784668238431</v>
+      </c>
+      <c r="AC6">
+        <v>-0.08466784668238431</v>
+      </c>
+      <c r="AD6">
+        <v>1613.2</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>1613.2</v>
+      </c>
+      <c r="AG6">
+        <v>-309.7</v>
+      </c>
+      <c r="AH6">
+        <v>0.4655431143945516</v>
+      </c>
+      <c r="AI6">
+        <v>0.5637011670976309</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.200803994034883</v>
+      </c>
+      <c r="AK6">
+        <v>-0.3298540845670466</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Joint Stock Commercial Bank for Investment and Development of Vietnam (HOSE:BID)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.179</v>
+      </c>
+      <c r="E7">
+        <v>0.268</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>951.2</v>
+      </c>
+      <c r="L7">
+        <v>0.4162436548223351</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>-0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>-0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>448.6</v>
+      </c>
+      <c r="V7">
+        <v>0.04441100474205779</v>
+      </c>
+      <c r="W7">
+        <v>0.2021893931342332</v>
+      </c>
+      <c r="X7">
+        <v>0.1023068141155902</v>
+      </c>
+      <c r="Y7">
+        <v>0.09988257901864296</v>
+      </c>
+      <c r="Z7">
+        <v>2.422559101028304</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.08477155349616511</v>
+      </c>
+      <c r="AC7">
+        <v>-0.08477155349616511</v>
+      </c>
+      <c r="AD7">
+        <v>9087.1</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>9087.1</v>
+      </c>
+      <c r="AG7">
+        <v>8638.5</v>
+      </c>
+      <c r="AH7">
+        <v>0.4735775111787452</v>
+      </c>
+      <c r="AI7">
+        <v>0.617116352350748</v>
+      </c>
+      <c r="AJ7">
+        <v>0.4609756878481931</v>
+      </c>
+      <c r="AK7">
+        <v>0.6050852800056036</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Asia Commercial Joint Stock Bank (HOSE:ACB)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.168</v>
+      </c>
+      <c r="E8">
+        <v>0.228</v>
+      </c>
+      <c r="F8">
+        <v>0.16</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>661.8</v>
+      </c>
+      <c r="L8">
+        <v>0.5150194552529183</v>
+      </c>
+      <c r="M8">
+        <v>158.2</v>
+      </c>
+      <c r="N8">
+        <v>0.03519935920256319</v>
+      </c>
+      <c r="O8">
+        <v>0.2390450287095799</v>
+      </c>
+      <c r="P8">
+        <v>158.2</v>
+      </c>
+      <c r="Q8">
+        <v>0.03519935920256319</v>
+      </c>
+      <c r="R8">
+        <v>0.2390450287095799</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>3835.9</v>
+      </c>
+      <c r="V8">
+        <v>0.8534843360626558</v>
+      </c>
+      <c r="W8">
+        <v>0.2405058690991024</v>
+      </c>
+      <c r="X8">
+        <v>0.1035091613603209</v>
+      </c>
+      <c r="Y8">
+        <v>0.1369967077387815</v>
+      </c>
+      <c r="Z8">
+        <v>1.403604587657018</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.08493131771170923</v>
+      </c>
+      <c r="AC8">
+        <v>-0.08493131771170923</v>
+      </c>
+      <c r="AD8">
+        <v>4248.8</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>4248.8</v>
+      </c>
+      <c r="AG8">
+        <v>412.9000000000001</v>
+      </c>
+      <c r="AH8">
+        <v>0.4859547991582029</v>
+      </c>
+      <c r="AI8">
+        <v>0.5695366013860405</v>
+      </c>
+      <c r="AJ8">
+        <v>0.08413995476127405</v>
+      </c>
+      <c r="AK8">
+        <v>0.1139285911373545</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Vietnam Prosperity Joint Stock Commercial Bank (HOSE:VPB)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0567</v>
+      </c>
+      <c r="E9">
+        <v>0.09820000000000001</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>534</v>
+      </c>
+      <c r="L9">
+        <v>0.4519678374947101</v>
+      </c>
+      <c r="M9">
+        <v>646.3</v>
+      </c>
+      <c r="N9">
+        <v>0.1087882307394503</v>
+      </c>
+      <c r="O9">
+        <v>1.210299625468165</v>
+      </c>
+      <c r="P9">
+        <v>646.3</v>
+      </c>
+      <c r="Q9">
+        <v>0.1087882307394503</v>
+      </c>
+      <c r="R9">
+        <v>1.210299625468165</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>4303.4</v>
+      </c>
+      <c r="V9">
+        <v>0.7243683616960394</v>
+      </c>
+      <c r="W9">
+        <v>0.1236941465335526</v>
+      </c>
+      <c r="X9">
+        <v>0.1038075886038462</v>
+      </c>
+      <c r="Y9">
+        <v>0.01988655792970637</v>
+      </c>
+      <c r="Z9">
+        <v>0.254846725278897</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.08496981479764915</v>
+      </c>
+      <c r="AC9">
+        <v>-0.08496981479764915</v>
+      </c>
+      <c r="AD9">
+        <v>5683.7</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>5683.7</v>
+      </c>
+      <c r="AG9">
+        <v>1380.3</v>
+      </c>
+      <c r="AH9">
+        <v>0.4889372537549679</v>
+      </c>
+      <c r="AI9">
+        <v>0.495251124045868</v>
+      </c>
+      <c r="AJ9">
+        <v>0.1885346664481233</v>
+      </c>
+      <c r="AK9">
+        <v>0.1924299456294438</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tien Phong Commercial Joint Stock Bank (HOSE:TPB)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.144</v>
+      </c>
+      <c r="E10">
+        <v>0.148</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>198</v>
+      </c>
+      <c r="L10">
+        <v>0.391304347826087</v>
+      </c>
+      <c r="M10">
+        <v>44.8</v>
+      </c>
+      <c r="N10">
+        <v>0.02611331312660294</v>
+      </c>
+      <c r="O10">
+        <v>0.2262626262626262</v>
+      </c>
+      <c r="P10">
+        <v>44.8</v>
+      </c>
+      <c r="Q10">
+        <v>0.02611331312660294</v>
+      </c>
+      <c r="R10">
+        <v>0.2262626262626262</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>1781.3</v>
+      </c>
+      <c r="V10">
+        <v>1.038295640009326</v>
+      </c>
+      <c r="W10">
+        <v>0.1484814398200225</v>
+      </c>
+      <c r="X10">
+        <v>0.1086199210563043</v>
+      </c>
+      <c r="Y10">
+        <v>0.03986151876371821</v>
+      </c>
+      <c r="Z10">
+        <v>0.6198701457797378</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.08553419965828096</v>
+      </c>
+      <c r="AC10">
+        <v>-0.08553419965828096</v>
+      </c>
+      <c r="AD10">
+        <v>1955.4</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>1955.4</v>
+      </c>
+      <c r="AG10">
+        <v>174.1000000000001</v>
+      </c>
+      <c r="AH10">
+        <v>0.5326614001634432</v>
+      </c>
+      <c r="AI10">
+        <v>0.5693902510046008</v>
+      </c>
+      <c r="AJ10">
+        <v>0.09213102608879724</v>
+      </c>
+      <c r="AK10">
+        <v>0.105330026014883</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Military Commercial Joint Stock Bank (HOSE:MBB)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.169</v>
+      </c>
+      <c r="E11">
+        <v>0.24</v>
+      </c>
+      <c r="F11">
+        <v>0.18</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>868.9</v>
+      </c>
+      <c r="L11">
+        <v>0.5076833187262635</v>
+      </c>
+      <c r="M11">
+        <v>107.7</v>
+      </c>
+      <c r="N11">
+        <v>0.02080958361510965</v>
+      </c>
+      <c r="O11">
+        <v>0.1239498216135344</v>
+      </c>
+      <c r="P11">
+        <v>107.7</v>
+      </c>
+      <c r="Q11">
+        <v>0.02080958361510965</v>
+      </c>
+      <c r="R11">
+        <v>0.1239498216135344</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>2745.7</v>
+      </c>
+      <c r="V11">
+        <v>0.5305187904550285</v>
+      </c>
+      <c r="W11">
+        <v>0.2402001437496544</v>
+      </c>
+      <c r="X11">
+        <v>0.111373249238326</v>
+      </c>
+      <c r="Y11">
+        <v>0.1288268945113284</v>
+      </c>
+      <c r="Z11">
+        <v>0.2023978857432892</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.08581570102328993</v>
+      </c>
+      <c r="AC11">
+        <v>-0.08581570102328993</v>
+      </c>
+      <c r="AD11">
+        <v>6441</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>6441</v>
+      </c>
+      <c r="AG11">
+        <v>3695.3</v>
+      </c>
+      <c r="AH11">
+        <v>0.5544699350062411</v>
+      </c>
+      <c r="AI11">
+        <v>0.5897433549722112</v>
+      </c>
+      <c r="AJ11">
+        <v>0.4165689678495739</v>
+      </c>
+      <c r="AK11">
+        <v>0.4519691780821918</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vietnam Joint Stock Commercial Bank for Industry and Trade (HOSE:CTG)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.182</v>
+      </c>
+      <c r="E12">
+        <v>0.293</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>878.9</v>
+      </c>
+      <c r="L12">
+        <v>0.4370245139475909</v>
+      </c>
+      <c r="M12">
+        <v>-0</v>
+      </c>
+      <c r="N12">
+        <v>-0</v>
+      </c>
+      <c r="O12">
+        <v>-0</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>-0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>14058.8</v>
+      </c>
+      <c r="V12">
+        <v>1.775908241119701</v>
+      </c>
+      <c r="W12">
+        <v>0.1761534453040446</v>
+      </c>
+      <c r="X12">
+        <v>0.1129588277996204</v>
+      </c>
+      <c r="Y12">
+        <v>0.06319461750442415</v>
+      </c>
+      <c r="Z12">
+        <v>2.092715920915713</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.08596620178453532</v>
+      </c>
+      <c r="AC12">
+        <v>-0.08596620178453532</v>
+      </c>
+      <c r="AD12">
+        <v>10329.6</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>10329.6</v>
+      </c>
+      <c r="AG12">
+        <v>-3729.199999999999</v>
+      </c>
+      <c r="AH12">
+        <v>0.5661295626438672</v>
+      </c>
+      <c r="AI12">
+        <v>0.6427358085531352</v>
+      </c>
+      <c r="AJ12">
+        <v>-0.890619029423003</v>
+      </c>
+      <c r="AK12">
+        <v>-1.853018633540371</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Saigon - Hanoi Commercial Joint Stock Bank (HOSE:SHB)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.163</v>
+      </c>
+      <c r="E13">
+        <v>0.271</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>312.3</v>
+      </c>
+      <c r="L13">
+        <v>0.5303107488537953</v>
+      </c>
+      <c r="M13">
+        <v>208.53</v>
+      </c>
+      <c r="N13">
+        <v>0.1424385245901639</v>
+      </c>
+      <c r="O13">
+        <v>0.6677233429394812</v>
+      </c>
+      <c r="P13">
+        <v>1.43</v>
+      </c>
+      <c r="Q13">
+        <v>0.000976775956284153</v>
+      </c>
+      <c r="R13">
+        <v>0.004578930515529939</v>
+      </c>
+      <c r="S13">
+        <v>207.1</v>
+      </c>
+      <c r="T13">
+        <v>0.9931424735050113</v>
+      </c>
+      <c r="U13">
+        <v>3210.6</v>
+      </c>
+      <c r="V13">
+        <v>2.193032786885246</v>
+      </c>
+      <c r="W13">
+        <v>0.1531407836022164</v>
+      </c>
+      <c r="X13">
+        <v>0.1147152552433038</v>
+      </c>
+      <c r="Y13">
+        <v>0.03842552835891264</v>
+      </c>
+      <c r="Z13">
+        <v>0.3561320754716981</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.08612398215867069</v>
+      </c>
+      <c r="AC13">
+        <v>-0.08612398215867069</v>
+      </c>
+      <c r="AD13">
+        <v>2008.1</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>2008.1</v>
+      </c>
+      <c r="AG13">
+        <v>-1202.5</v>
+      </c>
+      <c r="AH13">
+        <v>0.5783531580311627</v>
+      </c>
+      <c r="AI13">
+        <v>0.4693357640349646</v>
+      </c>
+      <c r="AJ13">
+        <v>-4.598470363288719</v>
+      </c>
+      <c r="AK13">
+        <v>-1.125936329588015</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Orient Commercial Joint Stock Bank (HOSE:OCB)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>89.2</v>
+      </c>
+      <c r="L14">
+        <v>0.3386484434320425</v>
+      </c>
+      <c r="M14">
+        <v>0.001</v>
+      </c>
+      <c r="N14">
+        <v>9.121590805436468E-07</v>
+      </c>
+      <c r="O14">
+        <v>1.121076233183856E-05</v>
+      </c>
+      <c r="P14">
+        <v>0.001</v>
+      </c>
+      <c r="Q14">
+        <v>9.121590805436468E-07</v>
+      </c>
+      <c r="R14">
+        <v>1.121076233183856E-05</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>34.1</v>
+      </c>
+      <c r="V14">
+        <v>0.03110462464653836</v>
+      </c>
+      <c r="W14">
+        <v>0.07591489361702128</v>
+      </c>
+      <c r="X14">
+        <v>0.1208909210077684</v>
+      </c>
+      <c r="Y14">
+        <v>-0.04497602739074708</v>
+      </c>
+      <c r="Z14">
+        <v>0.1540440961459734</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.08661452220524396</v>
+      </c>
+      <c r="AC14">
+        <v>-0.08661452220524396</v>
+      </c>
+      <c r="AD14">
+        <v>1761.3</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>1761.3</v>
+      </c>
+      <c r="AG14">
+        <v>1727.2</v>
+      </c>
+      <c r="AH14">
+        <v>0.6163563829787234</v>
+      </c>
+      <c r="AI14">
+        <v>0.5864744272775706</v>
+      </c>
+      <c r="AJ14">
+        <v>0.611723038781654</v>
+      </c>
+      <c r="AK14">
+        <v>0.5817251018827253</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Vietnam Maritime Commercial Joint Stock Bank (HOSE:MSB)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>178.6</v>
+      </c>
+      <c r="L15">
+        <v>0.4123758947125375</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>-0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>-0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>2001.6</v>
+      </c>
+      <c r="V15">
+        <v>1.694404469652078</v>
+      </c>
+      <c r="W15">
+        <v>0.1426745486499441</v>
+      </c>
+      <c r="X15">
+        <v>0.1344169209322677</v>
+      </c>
+      <c r="Y15">
+        <v>0.00825762771767638</v>
+      </c>
+      <c r="Z15">
+        <v>0.6284599032134026</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.08743091333942954</v>
+      </c>
+      <c r="AC15">
+        <v>-0.08743091333942954</v>
+      </c>
+      <c r="AD15">
+        <v>2505.7</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>2505.7</v>
+      </c>
+      <c r="AG15">
+        <v>504.0999999999999</v>
+      </c>
+      <c r="AH15">
+        <v>0.6796040141036073</v>
+      </c>
+      <c r="AI15">
+        <v>0.6358837710950387</v>
+      </c>
+      <c r="AJ15">
+        <v>0.2990981369407855</v>
+      </c>
+      <c r="AK15">
+        <v>0.2599927794110062</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nam A Commercial Joint Stock Bank (HOSE:NAB)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>124.8</v>
+      </c>
+      <c r="L16">
+        <v>0.4097176625082075</v>
+      </c>
+      <c r="M16">
+        <v>0.006</v>
+      </c>
+      <c r="N16">
+        <v>7.293059438434423E-06</v>
+      </c>
+      <c r="O16">
+        <v>4.807692307692308E-05</v>
+      </c>
+      <c r="P16">
+        <v>0.006</v>
+      </c>
+      <c r="Q16">
+        <v>7.293059438434423E-06</v>
+      </c>
+      <c r="R16">
+        <v>4.807692307692308E-05</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>49.4</v>
+      </c>
+      <c r="V16">
+        <v>0.06004618937644341</v>
+      </c>
+      <c r="W16">
+        <v>0.213369806804582</v>
+      </c>
+      <c r="X16">
+        <v>0.108511480403794</v>
+      </c>
+      <c r="Y16">
+        <v>0.104858326400788</v>
+      </c>
+      <c r="Z16">
+        <v>0.5147009124704293</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.08807498913532263</v>
+      </c>
+      <c r="AC16">
+        <v>-0.08807498913532263</v>
+      </c>
+      <c r="AD16">
+        <v>934.3</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>934.3</v>
+      </c>
+      <c r="AG16">
+        <v>884.9</v>
+      </c>
+      <c r="AH16">
+        <v>0.5317586795674445</v>
+      </c>
+      <c r="AI16">
+        <v>0.5839010061871133</v>
+      </c>
+      <c r="AJ16">
+        <v>0.5182126961817756</v>
+      </c>
+      <c r="AK16">
+        <v>0.5706455149287419</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>Vietnam Technological and Commercial Joint Stock Bank (HOSE:TCB)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D17">
         <v>0.179</v>
       </c>
-      <c r="E3">
+      <c r="E17">
         <v>0.194</v>
       </c>
-      <c r="F3">
+      <c r="F17">
         <v>0.24</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
         <v>920</v>
       </c>
-      <c r="L3">
+      <c r="L17">
         <v>0.5271602108640844</v>
       </c>
-      <c r="M3">
+      <c r="M17">
         <v>212.2</v>
       </c>
-      <c r="N3">
+      <c r="N17">
         <v>0.03124355840866928</v>
       </c>
-      <c r="O3">
+      <c r="O17">
         <v>0.2306521739130435</v>
       </c>
-      <c r="P3">
+      <c r="P17">
         <v>212.2</v>
       </c>
-      <c r="Q3">
+      <c r="Q17">
         <v>0.03124355840866928</v>
       </c>
-      <c r="R3">
+      <c r="R17">
         <v>0.2306521739130435</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
         <v>3359.6</v>
       </c>
-      <c r="V3">
+      <c r="V17">
         <v>0.4946553196501663</v>
       </c>
-      <c r="W3">
+      <c r="W17">
         <v>0.1775205016883743</v>
       </c>
-      <c r="X3">
-        <v>0.1095705542703871</v>
-      </c>
-      <c r="Y3">
-        <v>0.06794994741798718</v>
-      </c>
-      <c r="Z3">
+      <c r="X17">
+        <v>0.1095641743080625</v>
+      </c>
+      <c r="Y17">
+        <v>0.06795632738031185</v>
+      </c>
+      <c r="Z17">
         <v>0.1895493695083143</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.0926400152259272</v>
-      </c>
-      <c r="AC3">
-        <v>-0.0926400152259272</v>
-      </c>
-      <c r="AD3">
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.09263708284984584</v>
+      </c>
+      <c r="AC17">
+        <v>-0.09263708284984584</v>
+      </c>
+      <c r="AD17">
         <v>7985.1</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
         <v>7985.1</v>
       </c>
-      <c r="AG3">
+      <c r="AG17">
         <v>4625.5</v>
       </c>
-      <c r="AH3">
+      <c r="AH17">
         <v>0.5403772103756539</v>
       </c>
-      <c r="AI3">
+      <c r="AI17">
         <v>0.5759385480904469</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ17">
         <v>0.4051308102616206</v>
       </c>
-      <c r="AK3">
+      <c r="AK17">
         <v>0.4403183276375787</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
         <v>0</v>
       </c>
     </row>
